--- a/Result/profitability/5340.xlsx
+++ b/Result/profitability/5340.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.22</v>
+        <v>0.27125</v>
       </c>
       <c r="N2" t="n">
-        <v>14.995</v>
+        <v>16.2575</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2025</v>
+        <v>0.23375</v>
       </c>
       <c r="N3" t="n">
-        <v>14.77</v>
+        <v>15.64</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.16375</v>
+        <v>0.1975</v>
       </c>
       <c r="N4" t="n">
-        <v>13.01875</v>
+        <v>13.79</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09625</v>
+        <v>0.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3.693750000000001</v>
+        <v>4.53625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03749999999999999</v>
+        <v>0.05375000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.444999999999999</v>
+        <v>-3.18125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.045</v>
+        <v>-0.02874999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.6925</v>
+        <v>-7.33125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1175</v>
+        <v>-0.1075</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.79</v>
+        <v>-11.565</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.06625</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.107499999999998</v>
+        <v>-9.107500000000002</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>706</v>
+      </c>
+      <c r="D75" t="n">
+        <v>544</v>
+      </c>
+      <c r="E75" t="n">
+        <v>162</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>130</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.39%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>133</v>
+      </c>
+      <c r="K75" t="n">
+        <v>106</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.39375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.173913043478261</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.799999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0849457291175082</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.909090909090909</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.739999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4147692307692308</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
